--- a/output/pdf_financials_xlsx/SNAG.xlsx
+++ b/output/pdf_financials_xlsx/SNAG.xlsx
@@ -5056,19 +5056,19 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.377941</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.582095</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.614049</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.677044</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.903068</v>
       </c>
       <c r="I92" s="1" t="inlineStr">
         <is>
@@ -5076,19 +5076,19 @@
         </is>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.229886</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.745186</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.745186</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>4.131153</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.27829</v>
       </c>
     </row>
     <row r="93">
@@ -8098,7 +8098,11 @@
           <t>Reserves 7,8</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -9723,7 +9727,11 @@
           <t>Reserves 7, 8</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -10697,7 +10705,11 @@
           <t>Reserves 9, 10</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -12691,7 +12703,11 @@
           <t>Reserves 9, 10 2,377,941</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -21463,7 +21479,7 @@
         <v>-2.05199</v>
       </c>
       <c r="P189" s="5" t="n">
-        <v>0.029407</v>
+        <v>-0.029407</v>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
@@ -24647,7 +24663,7 @@
         <v>-1.056142</v>
       </c>
       <c r="N229" s="5" t="n">
-        <v>0.00238</v>
+        <v>-0.00238</v>
       </c>
       <c r="O229" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/SNAG.xlsx
+++ b/output/pdf_financials_xlsx/SNAG.xlsx
@@ -2000,19 +2000,19 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.421699</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.037318</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.006599</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.322984</v>
       </c>
       <c r="I34" s="1" t="inlineStr">
         <is>
@@ -2020,19 +2020,19 @@
         </is>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.412676</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.403093</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.135203</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.709647</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.828062</v>
       </c>
     </row>
     <row r="35">
@@ -2104,19 +2104,19 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.001625</v>
+        <v>0.018625</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.421699</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.037318</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.006599</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.322984</v>
       </c>
       <c r="I36" s="1" t="inlineStr">
         <is>
@@ -2124,19 +2124,19 @@
         </is>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.412676</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.161799</v>
+        <v>0.5648919999999999</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.0045</v>
+        <v>0.139703</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.709647</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.828062</v>
       </c>
     </row>
     <row r="37">
@@ -2728,19 +2728,19 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.02043</v>
+        <v>0.00343</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.42675</v>
+        <v>0.005051</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.049671</v>
+        <v>0.012353</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.00694</v>
+        <v>0.000341</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.668468</v>
+        <v>0.345484</v>
       </c>
       <c r="I48" s="1" t="inlineStr">
         <is>
@@ -2748,19 +2748,19 @@
         </is>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.563507</v>
+        <v>0.150831</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.744204</v>
+        <v>0.341111</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.1784</v>
+        <v>0.043197</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.815019</v>
+        <v>0.105372</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.287633</v>
+        <v>0.459571</v>
       </c>
     </row>
     <row r="49">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11604,7 +11604,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">

--- a/output/pdf_financials_xlsx/SNAG.xlsx
+++ b/output/pdf_financials_xlsx/SNAG.xlsx
@@ -679,43 +679,43 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.213169</v>
+        <v>0.235991</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.214878</v>
+        <v>0.231657</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.240415</v>
+        <v>0.279148</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.29738</v>
+        <v>0.350086</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.251613</v>
+        <v>0.309691</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.184269</v>
+        <v>0.220198</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.151576</v>
+        <v>0.170427</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.132582</v>
+        <v>0.151716</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.196902</v>
+        <v>0.210371</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.201414</v>
+        <v>0.217237</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.203984</v>
+        <v>0.224255</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.196727</v>
+        <v>0.222351</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.190978</v>
+        <v>0.221683</v>
       </c>
     </row>
     <row r="8">
@@ -1139,13 +1139,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.037</v>
+        <v>0.037</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0.035</v>
+        <v>0.035</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.532</v>
+        <v>-0.532</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002722</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -5926,16 +5926,16 @@
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>0.00335</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001702</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>0.024983</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>0.008652</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>0</v>
@@ -6131,10 +6131,10 @@
         <v>0</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.216232</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.020625</v>
       </c>
       <c r="N115" s="3" t="n">
         <v>0</v>
@@ -7001,7 +7001,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002722</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -7010,16 +7010,16 @@
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00335</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001702</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.024983</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.008652</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>0</v>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.599754</v>
+        <v>-0.602476</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.491613</v>
@@ -7056,16 +7056,16 @@
         <v>-0.584715</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.550721</v>
+        <v>-0.554071</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-0.837023</v>
+        <v>-0.8387250000000001</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-0.289751</v>
+        <v>-0.314734</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-0.770628</v>
+        <v>-0.77928</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>-0.656565</v>
@@ -14309,7 +14309,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -16437,7 +16441,11 @@
           <t>Sale / (purchase) of equipment</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -17580,7 +17588,11 @@
           <t>Deferred income tax (recovery)</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -18151,7 +18163,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E144" s="5" t="n">
         <v>-0.002722</v>
       </c>
@@ -18496,7 +18512,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E149" s="5" t="n">
         <v>0.022822</v>
       </c>
@@ -28355,7 +28375,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -29846,7 +29870,11 @@
           <t>Deferred income tax recovery (expense) 14</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E295" s="5" t="n">
         <v>-0.037</v>
       </c>
